--- a/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_d_deptot_a_2020.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_d_deptot_a_2020.xlsx
@@ -111,7 +111,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:07</t>
+    <t xml:space="preserve">2026-09-24 00:58</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -534,7 +534,7 @@
         <v>-0.38</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="3">
@@ -548,7 +548,7 @@
         <v>-0.59</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="4">
@@ -562,7 +562,7 @@
         <v>-0.29</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="5">
@@ -576,7 +576,7 @@
         <v>0.24</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="6">
@@ -590,7 +590,7 @@
         <v>0.35</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="7">
@@ -604,7 +604,7 @@
         <v>0.02</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="8">
@@ -615,10 +615,10 @@
         <v>11</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="9">
@@ -629,10 +629,10 @@
         <v>11</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="10">
@@ -646,7 +646,7 @@
         <v>-0.02</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="11">
@@ -660,7 +660,7 @@
         <v>-0.02</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="12">
@@ -674,7 +674,7 @@
         <v>0.26</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="13">
@@ -688,7 +688,7 @@
         <v>0.23</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="14">
@@ -702,7 +702,7 @@
         <v>0</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="15">
@@ -713,10 +713,10 @@
         <v>11</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.07</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="16">
@@ -727,10 +727,10 @@
         <v>11</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>-0.22</v>
+        <v>-0.23</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="17">
@@ -741,10 +741,10 @@
         <v>11</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>-0.29</v>
+        <v>-0.28</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="18">
@@ -758,7 +758,7 @@
         <v>-0.8</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="19">
@@ -769,10 +769,10 @@
         <v>25</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>0.39</v>
+        <v>0.36</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="20">
@@ -783,10 +783,10 @@
         <v>25</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>-0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="21">
@@ -800,7 +800,7 @@
         <v>0.16</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_d_deptot_a_2020.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_d_deptot_a_2020.xlsx
@@ -96,7 +96,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -111,7 +111,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:58</t>
+    <t xml:space="preserve">2026-10-01 23:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_d_deptot_a_2020.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_d_deptot_a_2020.xlsx
@@ -111,7 +111,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:05</t>
+    <t xml:space="preserve">2026-10-05 19:37</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
